--- a/data/trans_orig/IQ3004_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado</t>
+          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,08</t>
+          <t>6,34; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,33</t>
+          <t>6,94; 9,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,95</t>
+          <t>6,68; 9,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,89</t>
+          <t>6,45; 8,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,24 +707,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,89</t>
+          <t>6,36; 7,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,76</t>
+          <t>6,98; 8,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,75</t>
+          <t>6,03; 7,67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 8,33</t>
+          <t>6,94; 8,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 14,28</t>
+          <t>7,62; 13,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,44</t>
+          <t>7,58; 10,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,18</t>
+          <t>6,88; 8,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,45</t>
+          <t>6,7; 8,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,11</t>
+          <t>5,37; 8,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,03</t>
+          <t>7,14; 8,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,28</t>
+          <t>7,45; 11,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,07</t>
+          <t>6,91; 9,07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,27 +897,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,22</t>
+          <t>4,41; 8,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 9,32</t>
+          <t>7,69; 9,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,0</t>
+          <t>5,32; 6,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,75</t>
+          <t>4,56; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,62</t>
+          <t>6,45; 7,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,68</t>
+          <t>5,45; 7,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,32</t>
+          <t>7,26; 8,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,58</t>
+          <t>6,36; 7,59</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,45</t>
+          <t>5,59; 7,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,2</t>
+          <t>5,92; 8,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 11,08</t>
+          <t>8,63; 11,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,12</t>
+          <t>5,88; 7,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,28</t>
+          <t>7,24; 10,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,13</t>
+          <t>5,88; 7,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,11</t>
+          <t>6,09; 7,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,78</t>
+          <t>6,81; 8,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,24</t>
+          <t>7,08; 9,16</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1117,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,27</t>
+          <t>5,27; 7,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,58</t>
+          <t>7,1; 9,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,39</t>
+          <t>8,81; 13,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,31</t>
+          <t>6,36; 10,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,34</t>
+          <t>6,58; 10,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,11</t>
+          <t>4,52; 7,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,34</t>
+          <t>6,19; 8,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,56</t>
+          <t>7,07; 9,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,3</t>
+          <t>6,56; 10,25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,52</t>
+          <t>5,12; 7,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,56</t>
+          <t>6,0; 7,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,74</t>
+          <t>5,99; 7,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,23</t>
+          <t>6,48; 7,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,15</t>
+          <t>6,49; 8,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,28</t>
+          <t>5,65; 9,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,75; 7,25</t>
+          <t>5,92; 7,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,65</t>
+          <t>6,46; 7,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,03</t>
+          <t>6,05; 8,04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 8,38</t>
+          <t>6,27; 8,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,49</t>
+          <t>6,95; 8,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,32</t>
+          <t>6,82; 8,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,23</t>
+          <t>6,53; 8,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,93</t>
+          <t>7,1; 8,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,42</t>
+          <t>7,14; 11,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,95</t>
+          <t>6,62; 7,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,38</t>
+          <t>7,21; 8,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,24</t>
+          <t>7,16; 9,6</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,02; 9,03</t>
+          <t>7,07; 9,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,17</t>
+          <t>6,66; 8,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,55</t>
+          <t>7,33; 8,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,97</t>
+          <t>6,85; 9,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,93</t>
+          <t>7,17; 9,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 8,94</t>
+          <t>7,51; 8,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,6</t>
+          <t>7,08; 8,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,35</t>
+          <t>7,11; 8,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,43</t>
+          <t>7,51; 8,43</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,64</t>
+          <t>6,82; 7,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,57</t>
+          <t>7,39; 8,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,62</t>
+          <t>7,68; 8,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,6</t>
+          <t>6,85; 7,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,21</t>
+          <t>7,46; 8,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,91</t>
+          <t>6,82; 7,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,21</t>
+          <t>7,51; 8,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,03</t>
+          <t>7,38; 8,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Provincia-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,17</t>
+          <t>6,41; 10,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,3</t>
+          <t>6,97; 9,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,49</t>
+          <t>6,63; 9,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 6,65</t>
+          <t>6,09; 6,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,94</t>
+          <t>6,38; 8,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,29</t>
+          <t>5,61; 7,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,89</t>
+          <t>6,32; 7,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,76</t>
+          <t>7,04; 8,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,67</t>
+          <t>6,06; 7,72</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,27</t>
+          <t>6,99; 8,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 13,4</t>
+          <t>7,61; 14,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 10,45</t>
+          <t>7,48; 10,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,26</t>
+          <t>6,92; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,49</t>
+          <t>6,63; 8,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,37</t>
+          <t>5,36; 8,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,12</t>
+          <t>7,11; 8,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,89</t>
+          <t>7,46; 11,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 9,07</t>
+          <t>6,92; 9,25</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,1</t>
+          <t>4,39; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 9,25</t>
+          <t>7,75; 9,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,84</t>
+          <t>4,84; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,62</t>
+          <t>6,46; 7,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,26</t>
+          <t>7,15; 8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,67</t>
+          <t>5,32; 7,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,35</t>
+          <t>7,21; 8,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,59</t>
+          <t>6,37; 7,65</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 7,39</t>
+          <t>5,63; 7,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,27</t>
+          <t>5,93; 8,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,06</t>
+          <t>8,45; 11,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,11</t>
+          <t>5,89; 7,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,37</t>
+          <t>7,24; 10,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,19</t>
+          <t>5,83; 7,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,09</t>
+          <t>6,09; 7,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,78</t>
+          <t>6,88; 8,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,16</t>
+          <t>7,1; 9,1</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,21</t>
+          <t>5,38; 7,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,8</t>
+          <t>7,1; 9,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 13,57</t>
+          <t>8,92; 13,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1137,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,34</t>
+          <t>6,69; 10,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 7,06</t>
+          <t>4,58; 7,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,27</t>
+          <t>6,19; 8,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,43</t>
+          <t>7,2; 9,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,25</t>
+          <t>6,63; 10,32</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,62</t>
+          <t>5,14; 7,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,71</t>
+          <t>6,0; 7,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 7,76</t>
+          <t>5,91; 7,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 7,22</t>
+          <t>6,41; 7,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,03</t>
+          <t>6,48; 8,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,37</t>
+          <t>5,74; 9,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,26</t>
+          <t>6,0; 7,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,65</t>
+          <t>6,44; 7,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,04</t>
+          <t>6,04; 8,06</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,39</t>
+          <t>6,28; 8,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,35</t>
+          <t>6,88; 8,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,29</t>
+          <t>6,74; 8,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,3</t>
+          <t>6,55; 8,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,66</t>
+          <t>7,14; 8,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,28</t>
+          <t>7,13; 11,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,94</t>
+          <t>6,62; 7,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,34</t>
+          <t>7,22; 8,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,6</t>
+          <t>7,16; 9,55</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,22</t>
+          <t>7,01; 9,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,29</t>
+          <t>6,62; 8,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,5</t>
+          <t>7,29; 8,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,85; 9,0</t>
+          <t>6,87; 8,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,09</t>
+          <t>7,18; 8,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,84</t>
+          <t>7,47; 8,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,63</t>
+          <t>7,16; 8,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,29</t>
+          <t>7,14; 8,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,43</t>
+          <t>7,53; 8,42</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,65</t>
+          <t>6,79; 7,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,51</t>
+          <t>7,42; 8,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,6</t>
+          <t>7,68; 8,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,57</t>
+          <t>6,83; 7,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,23</t>
+          <t>7,38; 8,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,87</t>
+          <t>6,82; 7,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,48</t>
+          <t>6,91; 7,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,21</t>
+          <t>7,53; 8,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,06</t>
+          <t>7,34; 8,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,02</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,49</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,26</t>
+          <t>6,09; 6,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,65</t>
+          <t>6,42; 8,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,98</t>
+          <t>5,54; 7,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 6,64</t>
+          <t>6,36; 10,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,79</t>
+          <t>6,9; 9,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 7,32</t>
+          <t>6,68; 9,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,99</t>
+          <t>6,32; 7,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 8,84</t>
+          <t>6,97; 8,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,72</t>
+          <t>6,14; 7,75</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,36</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,46</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,57</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>9,24</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,66</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,5</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,46</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,3</t>
+          <t>6,86; 8,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 14,25</t>
+          <t>6,7; 8,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 10,72</t>
+          <t>5,3; 8,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,31</t>
+          <t>7,01; 8,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,59</t>
+          <t>7,61; 14,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,27</t>
+          <t>7,51; 10,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,04</t>
+          <t>7,14; 8,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,94</t>
+          <t>7,46; 11,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,25</t>
+          <t>6,89; 9,07</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,08</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,83</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,08</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,07</t>
+          <t>4,78; 7,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 9,31</t>
+          <t>6,46; 7,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,0</t>
+          <t>7,05; 8,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,84</t>
+          <t>4,46; 8,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,62</t>
+          <t>7,77; 9,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,26</t>
+          <t>5,3; 6,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,58</t>
+          <t>5,27; 7,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,29</t>
+          <t>7,24; 8,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,65</t>
+          <t>6,36; 7,58</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,55</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,49</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,81</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,96</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,49</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,49</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,47</t>
+          <t>5,86; 7,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,24</t>
+          <t>7,2; 10,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,08</t>
+          <t>5,83; 7,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,14</t>
+          <t>5,66; 7,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,46</t>
+          <t>5,88; 8,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,18</t>
+          <t>8,59; 11,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,07</t>
+          <t>6,07; 7,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,78</t>
+          <t>6,8; 8,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,1</t>
+          <t>7,16; 9,24</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,03</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,01</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,03</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,41</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,36</t>
+          <t>6,36; 10,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,86</t>
+          <t>6,76; 10,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,73</t>
+          <t>4,6; 7,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,07</t>
+          <t>5,38; 7,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,52</t>
+          <t>6,97; 9,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,07</t>
+          <t>8,92; 13,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,26</t>
+          <t>6,2; 8,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,54</t>
+          <t>7,18; 9,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,32</t>
+          <t>6,5; 10,3</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,87</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,28</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,78</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6,46</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,83</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,87</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,28</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,62</t>
+          <t>6,51; 7,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,55</t>
+          <t>6,55; 8,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,84</t>
+          <t>5,59; 9,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,23</t>
+          <t>4,88; 7,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,11</t>
+          <t>6,0; 7,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,14</t>
+          <t>5,82; 7,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,28</t>
+          <t>5,75; 7,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,61</t>
+          <t>6,49; 7,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,06</t>
+          <t>6,06; 8,03</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,89</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8,31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,37</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,89</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,45</t>
+          <t>6,51; 8,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,37</t>
+          <t>7,21; 8,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,15</t>
+          <t>7,14; 11,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,25</t>
+          <t>6,34; 8,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,75</t>
+          <t>6,93; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,96</t>
+          <t>6,81; 8,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,93</t>
+          <t>6,63; 7,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,28</t>
+          <t>7,24; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,55</t>
+          <t>7,19; 9,24</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7,69</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8,13</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,87</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>7,38</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>7,9</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,12</t>
+          <t>6,82; 8,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,19</t>
+          <t>7,15; 8,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,46</t>
+          <t>7,48; 8,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,97</t>
+          <t>7,02; 9,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,97</t>
+          <t>6,63; 8,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 8,9</t>
+          <t>7,37; 8,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,69</t>
+          <t>7,2; 8,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,39</t>
+          <t>7,15; 8,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,42</t>
+          <t>7,55; 8,43</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>7,79</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>8,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,65</t>
+          <t>6,85; 7,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,57</t>
+          <t>7,42; 8,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,59</t>
+          <t>6,85; 7,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,59</t>
+          <t>6,8; 7,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,17</t>
+          <t>7,37; 8,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,88</t>
+          <t>7,69; 8,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,47</t>
+          <t>6,95; 7,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,22</t>
+          <t>7,52; 8,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,34; 8,04</t>
+          <t>7,37; 8,03</t>
         </is>
       </c>
     </row>
